--- a/Configs/GameConfig/Datas/stacklands_unit.xlsx
+++ b/Configs/GameConfig/Datas/stacklands_unit.xlsx
@@ -2341,22 +2341,22 @@
         </is>
       </c>
       <c r="H12" s="13" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="N12" s="13" t="n">
         <v>0</v>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="Q12" s="13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="R12" s="13" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="S12" s="13" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>equip-mobs-md-2026-08-06</t>
         </is>
       </c>
       <c r="T12" s="14" t="inlineStr">
         <is>
-          <t>核对日期 2026-08-03；玩法推定值：依据字段语义和同类条目补齐，保证规则可执行</t>
+          <t>2026-08-06 按《Stacklands_Original版_装备与Mobs数值.md》校准攻速/命中/伤害/防御/暴击档位数值</t>
         </is>
       </c>
       <c r="U12" s="0" t="n">
@@ -2420,22 +2420,22 @@
         </is>
       </c>
       <c r="H13" s="13" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="N13" s="13" t="n">
         <v>1</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Q13" s="13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="R13" s="13" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="S13" s="13" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>equip-mobs-md-2026-08-06</t>
         </is>
       </c>
       <c r="T13" s="14" t="inlineStr">
         <is>
-          <t>核对日期 2026-08-03；玩法推定值：依据字段语义和同类条目补齐，保证规则可执行</t>
+          <t>2026-08-06 按《Stacklands_Original版_装备与Mobs数值.md》校准攻速/命中/伤害/防御/暴击档位数值</t>
         </is>
       </c>
       <c r="U13" s="0" t="n">
@@ -2499,22 +2499,22 @@
         </is>
       </c>
       <c r="H14" s="13" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>0.95</v>
+        <v>0.59</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="N14" s="13" t="n">
         <v>1</v>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="Q14" s="13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="R14" s="13" t="inlineStr">
@@ -2539,12 +2539,12 @@
       </c>
       <c r="S14" s="13" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>equip-mobs-md-2026-08-06</t>
         </is>
       </c>
       <c r="T14" s="14" t="inlineStr">
         <is>
-          <t>核对日期 2026-08-03；玩法推定值：依据字段语义和同类条目补齐，保证规则可执行</t>
+          <t>2026-08-06 按《Stacklands_Original版_装备与Mobs数值.md》校准攻速/命中/伤害/防御/暴击档位数值</t>
         </is>
       </c>
       <c r="U14" s="0" t="n">
@@ -2578,22 +2578,22 @@
         </is>
       </c>
       <c r="H15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="13" t="n">
         <v>0.8</v>
       </c>
-      <c r="I15" s="13" t="n">
-        <v>0.95</v>
-      </c>
       <c r="J15" s="13" t="n">
-        <v>174</v>
+        <v>5</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>349</v>
+        <v>6</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>173</v>
+        <v>2</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="N15" s="13" t="n">
         <v>0</v>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Q15" s="13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="R15" s="13" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S15" s="13" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>equip-mobs-md-2026-08-06</t>
         </is>
       </c>
       <c r="T15" s="14" t="inlineStr">
         <is>
-          <t>核对日期 2026-08-03；玩法推定值：依据字段语义和同类条目补齐，保证规则可执行</t>
+          <t>2026-08-06 按《Stacklands_Original版_装备与Mobs数值.md》校准攻速/命中/伤害/防御/暴击档位数值</t>
         </is>
       </c>
       <c r="U15" s="0" t="n">
@@ -2657,22 +2657,22 @@
         </is>
       </c>
       <c r="H16" s="13" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="N16" s="13" t="n">
         <v>0</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Q16" s="13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="R16" s="13" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="S16" s="13" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>equip-mobs-md-2026-08-06</t>
         </is>
       </c>
       <c r="T16" s="14" t="inlineStr">
         <is>
-          <t>核对日期 2026-08-03；玩法推定值：依据字段语义和同类条目补齐，保证规则可执行</t>
+          <t>2026-08-06 按《Stacklands_Original版_装备与Mobs数值.md》校准攻速/命中/伤害/防御/暴击档位数值</t>
         </is>
       </c>
       <c r="U16" s="0" t="n">
@@ -2736,22 +2736,22 @@
         </is>
       </c>
       <c r="H17" s="13" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K17" s="13" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="N17" s="13" t="n">
         <v>0</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Q17" s="13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="R17" s="13" t="inlineStr">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="S17" s="13" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>equip-mobs-md-2026-08-06</t>
         </is>
       </c>
       <c r="T17" s="14" t="inlineStr">
         <is>
-          <t>核对日期 2026-08-03；玩法推定值：依据字段语义和同类条目补齐，保证规则可执行</t>
+          <t>2026-08-06 按《Stacklands_Original版_装备与Mobs数值.md》校准攻速/命中/伤害/防御/暴击档位数值</t>
         </is>
       </c>
       <c r="U17" s="0" t="n">
@@ -2815,22 +2815,22 @@
         </is>
       </c>
       <c r="H18" s="13" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="N18" s="13" t="n">
         <v>1</v>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="Q18" s="13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="R18" s="13" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="S18" s="13" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>equip-mobs-md-2026-08-06</t>
         </is>
       </c>
       <c r="T18" s="14" t="inlineStr">
         <is>
-          <t>核对日期 2026-08-03；玩法推定值：依据字段语义和同类条目补齐，保证规则可执行</t>
+          <t>2026-08-06 按《Stacklands_Original版_装备与Mobs数值.md》校准攻速/命中/伤害/防御/暴击档位数值</t>
         </is>
       </c>
       <c r="U18" s="0" t="n">
@@ -2894,22 +2894,22 @@
         </is>
       </c>
       <c r="H19" s="13" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K19" s="13" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="N19" s="13" t="n">
         <v>0</v>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Q19" s="13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="R19" s="13" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="S19" s="13" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>equip-mobs-md-2026-08-06</t>
         </is>
       </c>
       <c r="T19" s="14" t="inlineStr">
         <is>
-          <t>核对日期 2026-08-03；玩法推定值：依据字段语义和同类条目补齐，保证规则可执行</t>
+          <t>2026-08-06 按《Stacklands_Original版_装备与Mobs数值.md》校准攻速/命中/伤害/防御/暴击档位数值</t>
         </is>
       </c>
       <c r="U19" s="0" t="n">
@@ -2973,19 +2973,19 @@
         </is>
       </c>
       <c r="H20" s="13" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M20" s="13" t="n">
         <v>0.05</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="Q20" s="13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="R20" s="13" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="S20" s="13" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>equip-mobs-md-2026-08-06</t>
         </is>
       </c>
       <c r="T20" s="14" t="inlineStr">
         <is>
-          <t>核对日期 2026-08-03；玩法推定值：依据字段语义和同类条目补齐，保证规则可执行</t>
+          <t>2026-08-06 按《Stacklands_Original版_装备与Mobs数值.md》校准攻速/命中/伤害/防御/暴击档位数值</t>
         </is>
       </c>
       <c r="U20" s="0" t="n">
@@ -3052,22 +3052,22 @@
         </is>
       </c>
       <c r="H21" s="13" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K21" s="13" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="N21" s="13" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Q21" s="13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="R21" s="13" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S21" s="13" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>equip-mobs-md-2026-08-06</t>
         </is>
       </c>
       <c r="T21" s="14" t="inlineStr">
         <is>
-          <t>核对日期 2026-08-03；玩法推定值：依据字段语义和同类条目补齐，保证规则可执行</t>
+          <t>2026-08-06 按《Stacklands_Original版_装备与Mobs数值.md》校准攻速/命中/伤害/防御/暴击档位数值</t>
         </is>
       </c>
       <c r="U21" s="0" t="n">
@@ -3131,22 +3131,22 @@
         </is>
       </c>
       <c r="H22" s="13" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="n">
         <v>0</v>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="Q22" s="13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="R22" s="13" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="S22" s="13" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>equip-mobs-md-2026-08-06</t>
         </is>
       </c>
       <c r="T22" s="14" t="inlineStr">
         <is>
-          <t>核对日期 2026-08-03；玩法推定值：依据字段语义和同类条目补齐，保证规则可执行</t>
+          <t>2026-08-06 按《Stacklands_Original版_装备与Mobs数值.md》校准攻速/命中/伤害/防御/暴击档位数值</t>
         </is>
       </c>
       <c r="U22" s="0" t="n">
@@ -3210,22 +3210,22 @@
         </is>
       </c>
       <c r="H23" s="13" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>160</v>
+        <v>3</v>
       </c>
       <c r="K23" s="13" t="n">
-        <v>321</v>
+        <v>4</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>159</v>
+        <v>2</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="Q23" s="13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="R23" s="13" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="S23" s="13" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>equip-mobs-md-2026-08-06</t>
         </is>
       </c>
       <c r="T23" s="14" t="inlineStr">
         <is>
-          <t>核对日期 2026-08-03；玩法推定值：依据字段语义和同类条目补齐，保证规则可执行</t>
+          <t>2026-08-06 按《Stacklands_Original版_装备与Mobs数值.md》校准攻速/命中/伤害/防御/暴击档位数值</t>
         </is>
       </c>
       <c r="U23" s="0" t="n">
@@ -3289,22 +3289,22 @@
         </is>
       </c>
       <c r="H24" s="16" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="I24" s="16" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="J24" s="16" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K24" s="16" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="L24" s="16" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="M24" s="16" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="N24" s="16" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="Q24" s="16" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="R24" s="16" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="S24" s="16" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>equip-mobs-md-2026-08-06</t>
         </is>
       </c>
       <c r="T24" s="17" t="inlineStr">
         <is>
-          <t>核对日期 2026-08-03；玩法推定值：依据字段语义和同类条目补齐，保证规则可执行</t>
+          <t>2026-08-06 按《Stacklands_Original版_装备与Mobs数值.md》校准攻速/命中/伤害/防御/暴击档位数值</t>
         </is>
       </c>
       <c r="U24" s="0" t="n">
